--- a/hasil/CLAHE/Run7/history.xlsx
+++ b/hasil/CLAHE/Run7/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,16 +460,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7011904716491699</v>
+        <v>0.7107142806053162</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8129629492759705</v>
+        <v>0.7388888597488403</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7236431837081909</v>
+        <v>0.7167646884918213</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4939240515232086</v>
+        <v>0.573725163936615</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8388888835906982</v>
+        <v>0.8349206447601318</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8407407402992249</v>
+        <v>0.8333333134651184</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4179814755916595</v>
+        <v>0.4358015656471252</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4306568503379822</v>
+        <v>0.4096924960613251</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.867460310459137</v>
+        <v>0.8742063641548157</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9129629731178284</v>
+        <v>0.8537036776542664</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3579621911048889</v>
+        <v>0.3452825248241425</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3074770867824554</v>
+        <v>0.3765014111995697</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8916666507720947</v>
+        <v>0.8857142925262451</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9074074029922485</v>
+        <v>0.894444465637207</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2987959682941437</v>
+        <v>0.2962064146995544</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2711649537086487</v>
+        <v>0.2999186515808105</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8928571343421936</v>
+        <v>0.8972222208976746</v>
       </c>
       <c r="C6" t="n">
-        <v>0.914814829826355</v>
+        <v>0.8999999761581421</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2804344892501831</v>
+        <v>0.2736677527427673</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2358762174844742</v>
+        <v>0.275403767824173</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.920634925365448</v>
+        <v>0.9123015999794006</v>
       </c>
       <c r="C7" t="n">
-        <v>0.855555534362793</v>
+        <v>0.9037036895751953</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2256588190793991</v>
+        <v>0.2497076541185379</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3547529280185699</v>
+        <v>0.2534083724021912</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.908730149269104</v>
+        <v>0.9166666865348816</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9333333373069763</v>
+        <v>0.8574073910713196</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2347002774477005</v>
+        <v>0.2342444509267807</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2023573070764542</v>
+        <v>0.3519149422645569</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.9095237851142883</v>
+        <v>0.9103174805641174</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9222221970558167</v>
+        <v>0.9203703999519348</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2397575527429581</v>
+        <v>0.2358062565326691</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2314694821834564</v>
+        <v>0.2367026060819626</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9146825671195984</v>
+        <v>0.9198412895202637</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9055555462837219</v>
+        <v>0.9388889074325562</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2206774950027466</v>
+        <v>0.2127306014299393</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2410805821418762</v>
+        <v>0.179424062371254</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.9257936477661133</v>
+        <v>0.9341269731521606</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9333333373069763</v>
+        <v>0.9425926208496094</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2119512408971786</v>
+        <v>0.2006474286317825</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2046616673469543</v>
+        <v>0.1660490781068802</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.9408730268478394</v>
+        <v>0.9269841313362122</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9037036895751953</v>
+        <v>0.9407407641410828</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1782446652650833</v>
+        <v>0.191549614071846</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2496461719274521</v>
+        <v>0.1981601417064667</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,203 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.9313492178916931</v>
+        <v>0.9230158925056458</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9222221970558167</v>
+        <v>0.9425926208496094</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1878357082605362</v>
+        <v>0.2051592916250229</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2073338478803635</v>
+        <v>0.1825120896100998</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.9337301850318909</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9388889074325562</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.171287015080452</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.1641820967197418</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.9265872836112976</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.9370370507240295</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.197013184428215</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.1516512781381607</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.9436507821083069</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.9481481313705444</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.1729389727115631</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.1309116631746292</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.9357143044471741</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.885185182094574</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.1757808327674866</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.3518963158130646</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.9337301850318909</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.9444444179534912</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.1777561604976654</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.1482860147953033</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.9420635104179382</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.9592592716217041</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.1713560223579407</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.1227968037128448</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.9452381134033203</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.9296296238899231</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.1561566591262817</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.1885290294885635</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0.9452381134033203</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.152532771229744</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.1326967477798462</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0.9523809552192688</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.9629629850387573</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.1372669488191605</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.1302298009395599</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0.9464285969734192</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.9481481313705444</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.1478068083524704</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.1400898993015289</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0.9396825432777405</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9407407641410828</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.1576182544231415</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.1530436128377914</v>
       </c>
     </row>
   </sheetData>
